--- a/docs/STM32F407ZGT6_M144Z-M4_引脚配置表.xlsx
+++ b/docs/STM32F407ZGT6_M144Z-M4_引脚配置表.xlsx
@@ -169,7 +169,18 @@
     <t>巡线控制</t>
   </si>
   <si>
-    <t>巡线模块总使能</t>
+    <r>
+      <t>巡线模块</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>红外使能</t>
+    </r>
   </si>
   <si>
     <t>GPIO_Output</t>
@@ -178,7 +189,7 @@
     <t>PE2</t>
   </si>
   <si>
-    <t>LINE_EN</t>
+    <t>IR_EN</t>
   </si>
   <si>
     <t>新增</t>
@@ -797,7 +808,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -840,6 +851,13 @@
     <font>
       <sz val="10"/>
       <name val="Carlito"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -999,6 +1017,12 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="44">
@@ -1566,156 +1590,156 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1858,6 +1882,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1891,7 +1918,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2701,7 +2728,7 @@
       <c r="B13" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="45" t="s">
+      <c r="C13" s="48" t="s">
         <v>46</v>
       </c>
       <c r="D13" s="46" t="s">
@@ -2724,7 +2751,7 @@
       <c r="A14" s="43">
         <v>10</v>
       </c>
-      <c r="B14" s="48" t="s">
+      <c r="B14" s="49" t="s">
         <v>52</v>
       </c>
       <c r="C14" s="45" t="s">
@@ -2750,7 +2777,7 @@
       <c r="A15" s="43">
         <v>11</v>
       </c>
-      <c r="B15" s="48" t="s">
+      <c r="B15" s="49" t="s">
         <v>52</v>
       </c>
       <c r="C15" s="45" t="s">
@@ -2776,7 +2803,7 @@
       <c r="A16" s="43">
         <v>12</v>
       </c>
-      <c r="B16" s="49" t="s">
+      <c r="B16" s="50" t="s">
         <v>62</v>
       </c>
       <c r="C16" s="45" t="s">
@@ -2802,7 +2829,7 @@
       <c r="A17" s="43">
         <v>13</v>
       </c>
-      <c r="B17" s="49" t="s">
+      <c r="B17" s="50" t="s">
         <v>62</v>
       </c>
       <c r="C17" s="45" t="s">
@@ -2828,7 +2855,7 @@
       <c r="A18" s="43">
         <v>14</v>
       </c>
-      <c r="B18" s="50" t="s">
+      <c r="B18" s="51" t="s">
         <v>74</v>
       </c>
       <c r="C18" s="45" t="s">
@@ -2854,7 +2881,7 @@
       <c r="A19" s="43">
         <v>15</v>
       </c>
-      <c r="B19" s="50" t="s">
+      <c r="B19" s="51" t="s">
         <v>74</v>
       </c>
       <c r="C19" s="45" t="s">
@@ -2880,7 +2907,7 @@
       <c r="A20" s="43">
         <v>16</v>
       </c>
-      <c r="B20" s="50" t="s">
+      <c r="B20" s="51" t="s">
         <v>84</v>
       </c>
       <c r="C20" s="45" t="s">
@@ -2906,7 +2933,7 @@
       <c r="A21" s="43">
         <v>17</v>
       </c>
-      <c r="B21" s="50" t="s">
+      <c r="B21" s="51" t="s">
         <v>84</v>
       </c>
       <c r="C21" s="45" t="s">
@@ -2932,7 +2959,7 @@
       <c r="A22" s="43">
         <v>18</v>
       </c>
-      <c r="B22" s="50" t="s">
+      <c r="B22" s="51" t="s">
         <v>95</v>
       </c>
       <c r="C22" s="45" t="s">
@@ -2958,7 +2985,7 @@
       <c r="A23" s="43">
         <v>19</v>
       </c>
-      <c r="B23" s="50" t="s">
+      <c r="B23" s="51" t="s">
         <v>95</v>
       </c>
       <c r="C23" s="45" t="s">
@@ -2984,7 +3011,7 @@
       <c r="A24" s="43">
         <v>20</v>
       </c>
-      <c r="B24" s="51" t="s">
+      <c r="B24" s="52" t="s">
         <v>107</v>
       </c>
       <c r="C24" s="45" t="s">
@@ -3010,7 +3037,7 @@
       <c r="A25" s="43">
         <v>21</v>
       </c>
-      <c r="B25" s="51" t="s">
+      <c r="B25" s="52" t="s">
         <v>107</v>
       </c>
       <c r="C25" s="45" t="s">
@@ -3036,7 +3063,7 @@
       <c r="A26" s="43">
         <v>22</v>
       </c>
-      <c r="B26" s="51" t="s">
+      <c r="B26" s="52" t="s">
         <v>117</v>
       </c>
       <c r="C26" s="45" t="s">
@@ -3062,7 +3089,7 @@
       <c r="A27" s="43">
         <v>23</v>
       </c>
-      <c r="B27" s="51" t="s">
+      <c r="B27" s="52" t="s">
         <v>117</v>
       </c>
       <c r="C27" s="45" t="s">
@@ -3088,7 +3115,7 @@
       <c r="A28" s="43">
         <v>24</v>
       </c>
-      <c r="B28" s="52" t="s">
+      <c r="B28" s="53" t="s">
         <v>127</v>
       </c>
       <c r="C28" s="45" t="s">
@@ -3114,7 +3141,7 @@
       <c r="A29" s="43">
         <v>25</v>
       </c>
-      <c r="B29" s="52" t="s">
+      <c r="B29" s="53" t="s">
         <v>127</v>
       </c>
       <c r="C29" s="45" t="s">
@@ -3140,7 +3167,7 @@
       <c r="A30" s="43">
         <v>26</v>
       </c>
-      <c r="B30" s="52" t="s">
+      <c r="B30" s="53" t="s">
         <v>137</v>
       </c>
       <c r="C30" s="45" t="s">
@@ -3166,7 +3193,7 @@
       <c r="A31" s="43">
         <v>27</v>
       </c>
-      <c r="B31" s="52" t="s">
+      <c r="B31" s="53" t="s">
         <v>143</v>
       </c>
       <c r="C31" s="45" t="s">
@@ -3192,7 +3219,7 @@
       <c r="A32" s="43">
         <v>28</v>
       </c>
-      <c r="B32" s="52" t="s">
+      <c r="B32" s="53" t="s">
         <v>143</v>
       </c>
       <c r="C32" s="45" t="s">
@@ -3218,7 +3245,7 @@
       <c r="A33" s="43">
         <v>29</v>
       </c>
-      <c r="B33" s="52" t="s">
+      <c r="B33" s="53" t="s">
         <v>143</v>
       </c>
       <c r="C33" s="45" t="s">
@@ -3244,7 +3271,7 @@
       <c r="A34" s="43">
         <v>30</v>
       </c>
-      <c r="B34" s="52" t="s">
+      <c r="B34" s="53" t="s">
         <v>143</v>
       </c>
       <c r="C34" s="45" t="s">
@@ -3270,7 +3297,7 @@
       <c r="A35" s="43">
         <v>31</v>
       </c>
-      <c r="B35" s="52" t="s">
+      <c r="B35" s="53" t="s">
         <v>157</v>
       </c>
       <c r="C35" s="45" t="s">
@@ -3296,7 +3323,7 @@
       <c r="A36" s="43">
         <v>32</v>
       </c>
-      <c r="B36" s="53" t="s">
+      <c r="B36" s="54" t="s">
         <v>163</v>
       </c>
       <c r="C36" s="45" t="s">
@@ -3319,24 +3346,24 @@
       </c>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="54"/>
-      <c r="B37" s="55"/>
-      <c r="C37" s="56"/>
-      <c r="D37" s="57"/>
-      <c r="E37" s="57"/>
-      <c r="F37" s="57"/>
-      <c r="G37" s="57"/>
-      <c r="H37" s="58"/>
+      <c r="A37" s="55"/>
+      <c r="B37" s="56"/>
+      <c r="C37" s="57"/>
+      <c r="D37" s="58"/>
+      <c r="E37" s="58"/>
+      <c r="F37" s="58"/>
+      <c r="G37" s="58"/>
+      <c r="H37" s="59"/>
     </row>
     <row r="39" ht="34" customHeight="1" spans="1:8">
-      <c r="A39" s="59"/>
-      <c r="B39" s="59"/>
-      <c r="C39" s="59"/>
-      <c r="D39" s="59"/>
-      <c r="E39" s="59"/>
-      <c r="F39" s="59"/>
-      <c r="G39" s="59"/>
-      <c r="H39" s="59"/>
+      <c r="A39" s="60"/>
+      <c r="B39" s="60"/>
+      <c r="C39" s="60"/>
+      <c r="D39" s="60"/>
+      <c r="E39" s="60"/>
+      <c r="F39" s="60"/>
+      <c r="G39" s="60"/>
+      <c r="H39" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="3">
